--- a/data_cost.xlsx
+++ b/data_cost.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\seadrive_root\张天翼_1\我的资料库\毕业设计\Materials\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139D18DD-199B-452A-9B20-0DD0F9FF0A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Industrial Parameters" sheetId="3" r:id="rId1"/>
@@ -20,16 +26,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>Category</t>
   </si>
@@ -236,20 +243,20 @@
   </si>
   <si>
     <t>strict</t>
+  </si>
+  <si>
+    <t>CPP electricity(CNY/kWh)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00;[Red]0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,366 +268,49 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -628,251 +318,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -889,7 +337,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -905,61 +353,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1244,14 +648,15 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.625" style="8" customWidth="1"/>
     <col min="2" max="2" width="15" style="8" customWidth="1"/>
@@ -1262,7 +667,7 @@
     <col min="7" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:6">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
@@ -1302,7 +707,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
@@ -1313,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="10">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E3" s="10">
         <v>0.08</v>
@@ -1322,7 +727,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
@@ -1342,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
@@ -1362,7 +767,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>14</v>
       </c>
@@ -1382,7 +787,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>16</v>
       </c>
@@ -1402,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
@@ -1422,7 +827,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>18</v>
       </c>
@@ -1442,7 +847,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>19</v>
       </c>
@@ -1462,7 +867,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -1482,7 +887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
@@ -1502,7 +907,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -1522,7 +927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -1542,7 +947,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>27</v>
       </c>
@@ -1550,19 +955,19 @@
         <v>28</v>
       </c>
       <c r="C15" s="5">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D15" s="5">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="E15" s="5">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="F15" s="5">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>29</v>
       </c>
@@ -1570,29 +975,29 @@
         <v>30</v>
       </c>
       <c r="C16" s="5">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="D16" s="5">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="E16" s="5">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="F16" s="5">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.375" style="3" customWidth="1"/>
     <col min="2" max="2" width="33.875" style="3" customWidth="1"/>
@@ -1600,13 +1005,11 @@
     <col min="4" max="4" width="18.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="20.875" style="3" customWidth="1"/>
     <col min="6" max="6" width="35.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="24.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="7" max="7" width="25.625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:9">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
@@ -1625,333 +1028,333 @@
       <c r="F1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="G1" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="6">
-        <v>88.9274988837286</v>
+        <v>88.927498883728603</v>
       </c>
       <c r="C2" s="5">
-        <v>0.100173181501278</v>
+        <v>0.10017318150127801</v>
       </c>
       <c r="D2" s="7">
-        <v>2143.85503588066</v>
+        <v>2143.8550358806601</v>
       </c>
       <c r="E2" s="7">
-        <v>746.019756629689</v>
+        <v>746.01975662968903</v>
       </c>
       <c r="F2" s="7">
         <v>1010.89662307289</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="G2" s="7">
+        <v>0.40724594616174042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="6">
-        <v>46.1326439547</v>
+        <v>46.132643954700001</v>
       </c>
       <c r="C3" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D3" s="7">
-        <v>2216.83733497447</v>
+        <v>2216.8373349744702</v>
       </c>
       <c r="E3" s="7">
-        <v>851.696368403416</v>
+        <v>851.69636840341605</v>
       </c>
       <c r="F3" s="7">
-        <v>1534.43834320854</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9">
+        <v>1534.4383432085399</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.40619885448459742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="6">
-        <v>617.196936682375</v>
+        <v>617.19693668237505</v>
       </c>
       <c r="C4" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D4" s="7">
-        <v>2162.10061065411</v>
+        <v>2162.1006106541099</v>
       </c>
       <c r="E4" s="7">
-        <v>749.066289581721</v>
+        <v>749.06628958172098</v>
       </c>
       <c r="F4" s="7">
-        <v>1356.18656464295</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9">
+        <v>1356.1865646429501</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.38345996039749808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="6">
-        <v>123.199001506935</v>
+        <v>123.19900150693501</v>
       </c>
       <c r="C5" s="5">
-        <v>0.0751298861259586</v>
+        <v>7.5129886125958598E-2</v>
       </c>
       <c r="D5" s="7">
-        <v>2454.02980702936</v>
+        <v>2454.0298070293602</v>
       </c>
       <c r="E5" s="7">
-        <v>964.989312557237</v>
+        <v>964.98931255723699</v>
       </c>
       <c r="F5" s="7">
-        <v>1934.41615971221</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:9">
+        <v>1934.4161597122099</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.35900356357069219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="6">
-        <v>713.791882484556</v>
+        <v>713.79188248455603</v>
       </c>
       <c r="C6" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D6" s="7">
         <v>2134.73224849393</v>
       </c>
       <c r="E6" s="7">
-        <v>740.402711499368</v>
+        <v>740.40271149936802</v>
       </c>
       <c r="F6" s="7">
-        <v>1622.73148785303</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9">
+        <v>1622.7314878530301</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.39675843692882329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="6">
-        <v>723.113855334333</v>
+        <v>723.11385533433304</v>
       </c>
       <c r="C7" s="5">
-        <v>0.116868711751491</v>
+        <v>0.11686871175149099</v>
       </c>
       <c r="D7" s="7">
-        <v>2162.10061065411</v>
+        <v>2162.1006106541099</v>
       </c>
       <c r="E7" s="7">
-        <v>734.138278116747</v>
+        <v>734.13827811674696</v>
       </c>
       <c r="F7" s="7">
         <v>1886.50779835652</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="G7" s="7">
+        <v>0.45076704331081358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="6">
-        <v>143.288425544667</v>
+        <v>143.28842554466701</v>
       </c>
       <c r="C8" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D8" s="7">
-        <v>2189.46897281429</v>
+        <v>2189.4689728142898</v>
       </c>
       <c r="E8" s="7">
-        <v>805.046332575372</v>
+        <v>805.04633257537205</v>
       </c>
       <c r="F8" s="7">
-        <v>1540.85493582686</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9">
+        <v>1540.8549358268599</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.33888202810239948</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="6">
-        <v>72.1622028115816</v>
+        <v>72.162202811581594</v>
       </c>
       <c r="C9" s="5">
-        <v>0.0751298861259586</v>
+        <v>7.5129886125958598E-2</v>
       </c>
       <c r="D9" s="7">
-        <v>2160.27605317676</v>
+        <v>2160.2760531767599</v>
       </c>
       <c r="E9" s="7">
         <v>727.3174293408</v>
       </c>
       <c r="F9" s="7">
-        <v>1235.51407775621</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9">
+        <v>1235.5140777562101</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.30695941768252372</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="6">
-        <v>42.5580050246133</v>
+        <v>42.558005024613301</v>
       </c>
       <c r="C10" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D10" s="7">
-        <v>2280.69684668156</v>
+        <v>2280.6968466815601</v>
       </c>
       <c r="E10" s="7">
-        <v>790.829178799209</v>
+        <v>790.82917879920899</v>
       </c>
       <c r="F10" s="7">
-        <v>2679.5389419775</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9">
+        <v>2679.5389419775001</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.34710101871636362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="6">
-        <v>48.351640644825</v>
+        <v>48.351640644824997</v>
       </c>
       <c r="C11" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D11" s="7">
         <v>2203.15315389438</v>
       </c>
       <c r="E11" s="7">
-        <v>777.944883189559</v>
+        <v>777.94488318955905</v>
       </c>
       <c r="F11" s="7">
         <v>1044.01065255192</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="G11" s="7">
+        <v>0.40158462679439211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B12" s="6">
-        <v>75.8154171846086</v>
+        <v>75.815417184608606</v>
       </c>
       <c r="C12" s="5">
-        <v>0.100173181501278</v>
+        <v>0.10017318150127801</v>
       </c>
       <c r="D12" s="7">
         <v>2166.66200434748</v>
       </c>
       <c r="E12" s="7">
-        <v>796.16061146527</v>
+        <v>796.16061146526999</v>
       </c>
       <c r="F12" s="7">
         <v>1014.9012155772</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="G12" s="7">
+        <v>0.43610906647469239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B13" s="6">
-        <v>188.10437359</v>
+        <v>188.10437358999999</v>
       </c>
       <c r="C13" s="5">
-        <v>0.100173181501278</v>
+        <v>0.10017318150127801</v>
       </c>
       <c r="D13" s="7">
-        <v>2125.60946110721</v>
+        <v>2125.6094611072099</v>
       </c>
       <c r="E13" s="7">
-        <v>812.154909463457</v>
+        <v>812.15490946345699</v>
       </c>
       <c r="F13" s="7">
-        <v>1223.5233188094</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9">
+        <v>1223.5233188094001</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.45557216018836272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="6">
-        <v>78.4113790758571</v>
+        <v>78.411379075857099</v>
       </c>
       <c r="C14" s="5">
-        <v>0.0417388256255326</v>
+        <v>4.1738825625532598E-2</v>
       </c>
       <c r="D14" s="7">
         <v>2200</v>
       </c>
       <c r="E14" s="7">
-        <v>787.528768101172</v>
+        <v>787.52876810117198</v>
       </c>
       <c r="F14" s="7">
-        <v>1484.16039545548</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:9">
+        <v>1484.1603954554801</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.19889353218336109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B15" s="6">
-        <v>100.465191977504</v>
+        <v>100.46519197750401</v>
       </c>
       <c r="C15" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D15" s="7">
-        <v>2121.04806741384</v>
+        <v>2121.0480674138398</v>
       </c>
       <c r="E15" s="7">
-        <v>726.56764373094</v>
+        <v>726.56764373093995</v>
       </c>
       <c r="F15" s="7">
-        <v>1116.95853350899</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9">
+        <v>1116.9585335089901</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.38982565354377052</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>51</v>
       </c>
@@ -1959,22 +1362,22 @@
         <v>236.53426926575</v>
       </c>
       <c r="C16" s="5">
-        <v>0.108520946626385</v>
+        <v>0.10852094662638501</v>
       </c>
       <c r="D16" s="7">
         <v>2200</v>
       </c>
       <c r="E16" s="7">
-        <v>795.716325409764</v>
+        <v>795.71632540976395</v>
       </c>
       <c r="F16" s="7">
-        <v>1101.37402743357</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9">
+        <v>1101.3740274335701</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.4528115722484034</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>52</v>
       </c>
@@ -1982,191 +1385,191 @@
         <v>101.20046627465</v>
       </c>
       <c r="C17" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D17" s="7">
         <v>2200</v>
       </c>
       <c r="E17" s="7">
-        <v>754.397722247781</v>
+        <v>754.39772224778096</v>
       </c>
       <c r="F17" s="7">
-        <v>2098.98639413802</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9">
+        <v>2098.9863941380199</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.37630156179525392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B18" s="6">
-        <v>71.4546836008393</v>
+        <v>71.454683600839303</v>
       </c>
       <c r="C18" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D18" s="7">
-        <v>2146.89596500957</v>
+        <v>2146.8959650095699</v>
       </c>
       <c r="E18" s="7">
-        <v>717.487803790432</v>
+        <v>717.48780379043205</v>
       </c>
       <c r="F18" s="7">
-        <v>1699.80178577923</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9">
+        <v>1699.8017857792299</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.36331271096622442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="6">
-        <v>116.377140429</v>
+        <v>116.37714042899999</v>
       </c>
       <c r="C19" s="5">
-        <v>0.0584343558757456</v>
+        <v>5.8434355875745601E-2</v>
       </c>
       <c r="D19" s="7">
         <v>2200</v>
       </c>
       <c r="E19" s="7">
-        <v>879.686389900241</v>
+        <v>879.68638990024101</v>
       </c>
       <c r="F19" s="7">
-        <v>1606.06673856196</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9">
+        <v>1606.0667385619599</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.27848106679033008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B20" s="6">
-        <v>213.641081569</v>
+        <v>213.64108156899999</v>
       </c>
       <c r="C20" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D20" s="7">
         <v>2371.92472054882</v>
       </c>
       <c r="E20" s="7">
-        <v>943.66358189299</v>
+        <v>943.66358189299001</v>
       </c>
       <c r="F20" s="7">
-        <v>1816.73710993825</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9">
+        <v>1816.7371099382499</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.33308873864983018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="6">
-        <v>65.20837102545</v>
+        <v>65.208371025450006</v>
       </c>
       <c r="C21" s="5">
-        <v>0.0667821210008521</v>
+        <v>6.6782121000852096E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>2253.32848452138</v>
+        <v>2253.3284845213798</v>
       </c>
       <c r="E21" s="7">
-        <v>877.909245678223</v>
+        <v>877.90924567822299</v>
       </c>
       <c r="F21" s="7">
         <v>1278.13533894993</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="G21" s="7">
+        <v>0.30831070303893682</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B22" s="6">
-        <v>91.2949638884318</v>
+        <v>91.294963888431795</v>
       </c>
       <c r="C22" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D22" s="7">
         <v>2121.69969508432</v>
       </c>
       <c r="E22" s="7">
-        <v>725.074842584443</v>
+        <v>725.07484258444299</v>
       </c>
       <c r="F22" s="7">
         <v>1127.60896593337</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="G22" s="7">
+        <v>0.39649971236259662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="6">
-        <v>247.3567200865</v>
+        <v>247.35672008649999</v>
       </c>
       <c r="C23" s="5">
-        <v>0.0918254163761717</v>
+        <v>9.1825416376171698E-2</v>
       </c>
       <c r="D23" s="7">
         <v>2098.24109894703</v>
       </c>
       <c r="E23" s="7">
-        <v>725.074842584443</v>
+        <v>725.07484258444299</v>
       </c>
       <c r="F23" s="7">
-        <v>1239.37116746747</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9">
+        <v>1239.3711674674701</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.36798121767466191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B24" s="6">
-        <v>27.9358459168318</v>
+        <v>27.935845916831799</v>
       </c>
       <c r="C24" s="5">
-        <v>0.0584343558757456</v>
+        <v>5.8434355875745601E-2</v>
       </c>
       <c r="D24" s="7">
-        <v>2212.27594128111</v>
+        <v>2212.2759412811101</v>
       </c>
       <c r="E24" s="7">
-        <v>790.506061667932</v>
+        <v>790.50606166793204</v>
       </c>
       <c r="F24" s="7">
-        <v>1143.22239231587</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9">
+        <v>1143.2223923158699</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0.28519931492182499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="6">
-        <v>129.4389954053</v>
+        <v>129.43899540530001</v>
       </c>
       <c r="C25" s="5">
-        <v>0.100173181501278</v>
+        <v>0.10017318150127801</v>
       </c>
       <c r="D25" s="7">
         <v>2239.64430344129</v>
@@ -2175,121 +1578,122 @@
         <v>837.923500682758</v>
       </c>
       <c r="F25" s="7">
-        <v>1652.46648505681</v>
-      </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:9">
+        <v>1652.4664850568099</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.42961656053797159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B26" s="6">
-        <v>38.0789637563667</v>
+        <v>38.078963756366697</v>
       </c>
       <c r="C26" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D26" s="7">
         <v>2134.73224849393</v>
       </c>
       <c r="E26" s="7">
-        <v>724.075198959553</v>
+        <v>724.07519895955295</v>
       </c>
       <c r="F26" s="7">
         <v>1194.06531259392</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="G26" s="7">
+        <v>0.37182802181394331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B27" s="6">
-        <v>61.4362289793314</v>
+        <v>61.436228979331403</v>
       </c>
       <c r="C27" s="5">
-        <v>0.0417388256255326</v>
+        <v>4.1738825625532598E-2</v>
       </c>
       <c r="D27" s="7">
-        <v>2376.48611424217</v>
+        <v>2376.4861142421701</v>
       </c>
       <c r="E27" s="7">
         <v>1068.50796348994</v>
       </c>
       <c r="F27" s="7">
-        <v>3422.21269539005</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" spans="1:9">
+        <v>3422.2126953900502</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.18942920480442901</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B28" s="6">
-        <v>437.852017840111</v>
+        <v>437.85201784011099</v>
       </c>
       <c r="C28" s="5">
-        <v>0.0834776512510652</v>
+        <v>8.3477651251065196E-2</v>
       </c>
       <c r="D28" s="7">
         <v>2198.59176020102</v>
       </c>
       <c r="E28" s="7">
-        <v>801.047758075824</v>
+        <v>801.04775807582405</v>
       </c>
       <c r="F28" s="7">
-        <v>2108.70330272585</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:9">
+        <v>2108.7033027258499</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.29669264265965167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B29" s="6">
-        <v>316.264594408667</v>
+        <v>316.26459440866699</v>
       </c>
       <c r="C29" s="5">
-        <v>0.100173181501278</v>
+        <v>0.10017318150127801</v>
       </c>
       <c r="D29" s="7">
-        <v>2125.60946110721</v>
+        <v>2125.6094611072099</v>
       </c>
       <c r="E29" s="7">
-        <v>749.066289581721</v>
+        <v>749.06628958172098</v>
       </c>
       <c r="F29" s="7">
         <v>1211.22137936833</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
+      <c r="G29" s="7">
+        <v>0.37920559692316591</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="10.625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:4">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
@@ -2303,7 +1707,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>2025</v>
       </c>
@@ -2317,7 +1721,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>2030</v>
       </c>
@@ -2331,7 +1735,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>2035</v>
       </c>
@@ -2345,7 +1749,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>2040</v>
       </c>
@@ -2359,7 +1763,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2045</v>
       </c>
@@ -2373,7 +1777,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>2050</v>
       </c>
@@ -2387,7 +1791,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>2055</v>
       </c>
@@ -2401,7 +1805,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>2060</v>
       </c>
@@ -2416,7 +1820,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>